--- a/docs/招生资料/25/衍生数据/中原工学院2025年本科招生章程-结构化附表.xlsx
+++ b/docs/招生资料/25/衍生数据/中原工学院2025年本科招生章程-结构化附表.xlsx
@@ -546,7 +546,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -613,7 +613,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -680,7 +680,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -747,7 +747,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -1685,7 +1685,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -1819,7 +1819,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1886,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -1953,7 +1953,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -2221,7 +2221,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -2288,7 +2288,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2422,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -2489,7 +2489,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -2623,7 +2623,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -3159,7 +3159,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -3293,7 +3293,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -3427,7 +3427,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -3494,7 +3494,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -3695,7 +3695,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -3762,7 +3762,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -3963,7 +3963,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -4030,7 +4030,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -4097,7 +4097,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -4164,7 +4164,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -4298,7 +4298,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -4365,7 +4365,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -4633,7 +4633,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -4700,7 +4700,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -4767,7 +4767,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -4968,7 +4968,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -5035,7 +5035,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -5102,7 +5102,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -5169,7 +5169,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -5236,7 +5236,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -5303,7 +5303,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
@@ -5370,7 +5370,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>2026-05-06T15:49:04</t>
+          <t>2026-05-07T21:13:37</t>
         </is>
       </c>
     </row>
